--- a/Excel/21_Advanced_Excel/Pinterest_Advanced_Excel_Practice.xlsx
+++ b/Excel/21_Advanced_Excel/Pinterest_Advanced_Excel_Practice.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Pinterest-Analytics-Project\Excel\21_Advanced_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05F0AC74-7B81-423A-88BA-31CEFD9A1613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5023FF-B067-4C02-8799-89196601F67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0A169DA0-D8EF-4A78-BB11-1808FFF7DD7F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{0A169DA0-D8EF-4A78-BB11-1808FFF7DD7F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,9 +36,122 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+  <si>
+    <t>Pinterest Link</t>
+  </si>
+  <si>
+    <t>Impressions</t>
+  </si>
+  <si>
+    <t>Engagement</t>
+  </si>
+  <si>
+    <t>Pin clicks</t>
+  </si>
+  <si>
+    <t>Outbound clicks</t>
+  </si>
+  <si>
+    <t>Saves</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>kitchen-organization-ideas</t>
+  </si>
+  <si>
+    <t>Kitchen</t>
+  </si>
+  <si>
+    <t>lunch-boxes-lunch-bags</t>
+  </si>
+  <si>
+    <t>home-decor</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>womens-fashion</t>
+  </si>
+  <si>
+    <t>Fashion</t>
+  </si>
+  <si>
+    <t>beauty-self-care</t>
+  </si>
+  <si>
+    <t>Beauty</t>
+  </si>
+  <si>
+    <t>kitchen-storage</t>
+  </si>
+  <si>
+    <t>handbag-fashion</t>
+  </si>
+  <si>
+    <t>home-essentials</t>
+  </si>
+  <si>
+    <t>skincare-products</t>
+  </si>
+  <si>
+    <t>desk-setup</t>
+  </si>
+  <si>
+    <t>Pinterest Analytics Summary</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>total Impressions</t>
+  </si>
+  <si>
+    <t>total Engagement</t>
+  </si>
+  <si>
+    <t>Total PinsClicks</t>
+  </si>
+  <si>
+    <t>Total Outbound clicks</t>
+  </si>
+  <si>
+    <t>Total Saves</t>
+  </si>
+  <si>
+    <t>Average Impressions</t>
+  </si>
+  <si>
+    <t>Maximum Impressions</t>
+  </si>
+  <si>
+    <t>Minimum Impressions</t>
+  </si>
+  <si>
+    <t>Engagement Rate</t>
+  </si>
+  <si>
+    <t>OutBound Click Rate</t>
+  </si>
+  <si>
+    <t>Total Impressions</t>
+  </si>
+  <si>
+    <t>Total Engagement</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -45,16 +159,78 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -62,17 +238,578 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -83,6 +820,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{38A1C451-CA34-4B5C-AD22-B4B268812C4B}" name="PinterestData" displayName="PinterestData" ref="A1:G11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:G11" xr:uid="{38A1C451-CA34-4B5C-AD22-B4B268812C4B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{A743A24B-73DD-4EC6-9499-7814D527C81B}" name="Pinterest Link" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{6DE57FB2-4F3B-4FCA-8C36-811517EE707E}" name="Impressions" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{88269E60-AA38-4881-8F30-2CC60DEB8471}" name="Engagement" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{E9D61BF4-8314-44A6-AC67-0D6E37B7AD4B}" name="Pin clicks" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{13E755A8-2B67-45C6-B0B2-827597C70E77}" name="Outbound clicks" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{6D45E09C-FC14-431B-B83C-7CDFC39954F9}" name="Saves" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{BD6B9865-8D59-4C9E-9AE0-AC824176738E}" name="Category" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +1155,459 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26C3FD3-E0F7-4D2A-9303-356C2A5CF46F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="7" width="22.26953125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3">
+        <v>214</v>
+      </c>
+      <c r="C2" s="3">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3">
+        <v>93</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3">
+        <v>76</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10">
+        <v>23</v>
+      </c>
+      <c r="C11" s="10">
+        <v>0</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F199CCCC-3E03-4668-9F22-A3C4DB01E1D4}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="28.54296875" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="13">
+        <f>SUM(PinterestData[Impressions])</f>
+        <v>647</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="13">
+        <f>SUM(PinterestData[Engagement])</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="13">
+        <f>SUM(PinterestData[Pin clicks])</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13">
+        <f>SUM(PinterestData[Outbound clicks])</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="13">
+        <f>SUM(PinterestData[Saves])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="13">
+        <f>AVERAGE(PinterestData[Impressions])</f>
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="13">
+        <f>MAX(PinterestData[Impressions])</f>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="13">
+        <f>MIN(PinterestData[Impressions])</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="14">
+        <f>B5/B4</f>
+        <v>2.3183925811437404E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="15">
+        <f>B7/B4</f>
+        <v>3.0911901081916537E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="26">
+        <f>SUMIF(PinterestData[Category],Analysis!A18,PinterestData[Impressions])</f>
+        <v>383</v>
+      </c>
+      <c r="C18" s="18">
+        <f>SUMIF(PinterestData[Category],Analysis!A18,PinterestData[Engagement])</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="16">
+        <f>SUMIF(PinterestData[Category],Analysis!A19,PinterestData[Impressions])</f>
+        <v>95</v>
+      </c>
+      <c r="C19" s="18">
+        <f>SUMIF(PinterestData[Category],Analysis!A19,PinterestData[Engagement])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="16">
+        <f>SUMIF(PinterestData[Category],Analysis!A20,PinterestData[Impressions])</f>
+        <v>83</v>
+      </c>
+      <c r="C20" s="18">
+        <f>SUMIF(PinterestData[Category],Analysis!A20,PinterestData[Engagement])</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="20">
+        <f>SUMIF(PinterestData[Category],Analysis!A21,PinterestData[Impressions])</f>
+        <v>86</v>
+      </c>
+      <c r="C21" s="21">
+        <f>SUMIF(PinterestData[Category],Analysis!A21,PinterestData[Engagement])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>